--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -487,18 +487,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="56" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>銀行</t>
@@ -524,10 +525,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>④客戶是否與銀行
+財管/信託相關
+(是/否)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>目前往來/交易狀況(原始資料)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>業務備註</t>
         </is>
@@ -544,6 +552,7 @@
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -554,12 +563,13 @@
       <c r="B3" s="5" t="inlineStr"/>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -570,12 +580,13 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>有開戶，TMU 透過財管下單（原標 自營）</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -586,12 +597,13 @@
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -602,12 +614,13 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -618,12 +631,13 @@
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -634,12 +648,13 @@
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營）</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -650,12 +665,13 @@
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -666,12 +682,13 @@
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營）</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -682,12 +699,13 @@
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -698,12 +716,13 @@
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -714,12 +733,13 @@
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>有開戶、久未交易（原標 自營）</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -730,12 +750,13 @@
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>有開戶（原標 自營）</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -746,12 +767,13 @@
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -762,12 +784,13 @@
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -778,12 +801,13 @@
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>有開戶（原標 銀行，未明確）</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -794,12 +818,13 @@
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>已取得債券授權交易（原標 銀行）</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -810,12 +835,13 @@
       <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -826,12 +852,13 @@
       <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -842,12 +869,13 @@
       <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -858,12 +886,13 @@
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>有股票戶，尚未有債券交易（原標 銀行）</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -876,6 +905,7 @@
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -886,12 +916,13 @@
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>待聯繫</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -902,12 +933,13 @@
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>已連繫，待下次遴選</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -918,12 +950,13 @@
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>已拜訪財管</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -934,12 +967,13 @@
       <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>已拜訪財管&amp;TMU</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -950,12 +984,13 @@
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>已拜訪TMU</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -966,12 +1001,13 @@
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>已拜訪財管&amp;信託基金</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -982,12 +1018,13 @@
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>已拜訪財管</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -998,12 +1035,13 @@
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>可透過自營(不提供負責人ID)</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1014,12 +1052,13 @@
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>已聯繫但目前不開戶</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1030,12 +1069,13 @@
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>透過自營，目前不開複委託</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1046,12 +1086,13 @@
       <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>透過自營，目前不開複委託</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1062,12 +1103,13 @@
       <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>已連繫，目前不做外幣債</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1078,12 +1120,13 @@
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1094,12 +1137,13 @@
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1110,12 +1154,13 @@
       <c r="B38" s="5" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1126,17 +1171,18 @@
       <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1148,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -1167,7 +1213,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>請協助重新釐清各銀行的「開戶狀況」與「開戶主體單位」，須逐家確認以下三件事：</t>
+          <t>請協助重新釐清各銀行的「開戶狀況」與「開戶主體單位」，須逐家確認以下四件事：</t>
         </is>
       </c>
     </row>
@@ -1235,36 +1281,53 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>⚠️ 重點：請勿再使用「銀行」「自營&amp;TMU」等籠統標註，務必明確到「財務部」或「TMU」。</t>
+          <t>4. 客戶是否與銀行財管 / 信託相關？（是 / 否）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理（財管）或信託部門通路，例如透過財管代為下單、或信託名義交易。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>特別需釐清：</t>
-        </is>
-      </c>
+      <c r="A17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>⚠️ 重點：請勿再使用「銀行」「自營&amp;TMU」等籠統標註，務必明確到「財務部」或「TMU」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>特別需釐清：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>• 上海銀行：標「亞灣區」意義不明，須確認屬財務部或 TMU。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>• 高雄、臺企銀、瑞興、永豐、第一：原僅標「銀行」，未區分主體，最需確認是否有 TMU。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>• 自營&amp;TMU 六家（元大、王道、新光、合庫、兆豐、安泰）：須確認是否兩單位各自開戶，或僅業務同時接觸。</t>
         </is>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>①有無開戶
+          <t>①主帳戶是否開戶
 (是/否/申請中)</t>
         </is>
       </c>
@@ -1223,7 +1223,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1. 客戶（銀行）有沒有在我司開戶？（是 / 否 / 申請中）</t>
+          <t>1. 客戶（銀行）主帳戶是否已在我司開戶？（是 / 否 / 申請中）</t>
         </is>
       </c>
     </row>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -1120,13 +1120,21 @@
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>總行 TIS，與銀行信託/財管無關</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -526,7 +526,7 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>④客戶是否與銀行
-財管/信託相關
+財務部/信託相關
 (是/否)</t>
         </is>
       </c>
@@ -583,7 +583,7 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>有開戶，TMU 透過財管下單（原標 自營）</t>
+          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -953,7 +953,7 @@
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財管</t>
+          <t>已拜訪財務部</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -970,7 +970,7 @@
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財管&amp;TMU</t>
+          <t>已拜訪財務部&amp;TMU</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財管&amp;信託基金</t>
+          <t>已拜訪財務部&amp;信託基金</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財管</t>
+          <t>已拜訪財務部</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>總行 TIS，與銀行信託/財管無關</t>
+          <t>總行 TIS，與銀行信託/財務部無關</t>
         </is>
       </c>
     </row>
@@ -1289,14 +1289,14 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>4. 客戶是否與銀行財管 / 信託相關？（是 / 否）</t>
+          <t>4. 客戶是否與銀行財務部 / 信託相關？（是 / 否）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理（財管）或信託部門通路，例如透過財管代為下單、或信託名義交易。</t>
+          <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理（財務部）或信託部門通路，例如透過財務部代為下單、或信託名義交易。</t>
         </is>
       </c>
     </row>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="13"/>
     </font>
@@ -54,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +74,41 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,13 +150,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -487,16 +548,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="56" customHeight="1">
@@ -507,35 +569,41 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>目前往來
+分類(A~G)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>①主帳戶是否開戶
 (是/否/申請中)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>②開戶主體
 (財務部/TMU/兩者皆有)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>③是否有TMU交易員
 (有/無→走財務部)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>④客戶是否與銀行
 財務部/信託相關
 (是/否)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>目前往來/交易狀況(原始資料)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>業務備註</t>
         </is>
@@ -553,6 +621,7 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -560,16 +629,21 @@
           <t>聯邦銀行</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -577,16 +651,21 @@
           <t>華南銀行</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -594,16 +673,21 @@
           <t>上海銀行</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -611,16 +695,21 @@
           <t>元大商業銀行</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -628,16 +717,21 @@
           <t>王道商業銀行</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -645,16 +739,21 @@
           <t>板信商銀</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營）</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -662,16 +761,21 @@
           <t>星展銀行</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -679,16 +783,21 @@
           <t>陽信商業銀行</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營）</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -696,16 +805,21 @@
           <t>新光銀行</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -713,16 +827,21 @@
           <t>台新銀行</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -730,16 +849,21 @@
           <t>華泰商業銀行</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>有開戶、久未交易（原標 自營）</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -747,16 +871,21 @@
           <t>京城銀行</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>有開戶（原標 自營）</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -764,16 +893,21 @@
           <t>合庫銀行</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -781,16 +915,21 @@
           <t>兆豐銀行</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -798,16 +937,21 @@
           <t>高雄銀行</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>有開戶（原標 銀行，未明確）</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -815,16 +959,21 @@
           <t>臺灣中小企業銀行</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>已取得債券授權交易（原標 銀行）</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -832,16 +981,21 @@
           <t>瑞興商業銀行</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -849,16 +1003,29 @@
           <t>永豐商業銀行</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>信託部已開戶</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -866,16 +1033,21 @@
           <t>安泰銀行</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -883,16 +1055,21 @@
           <t>第一商業銀行</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>有股票戶，尚未有債券交易（原標 銀行）</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -906,6 +1083,7 @@
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -913,16 +1091,21 @@
           <t>臺灣銀行</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>待聯繫</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -930,16 +1113,21 @@
           <t>中華郵政</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>已連繫，待下次遴選</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -947,16 +1135,21 @@
           <t>彰化商業銀行</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>已拜訪財務部</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -964,16 +1157,21 @@
           <t>台北富邦銀行</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>已拜訪財務部&amp;TMU</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -981,16 +1179,21 @@
           <t>中國信託商業銀行</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>已拜訪TMU</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -998,16 +1201,21 @@
           <t>遠東國際商業銀行</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>已拜訪財務部&amp;信託基金</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1015,16 +1223,21 @@
           <t>玉山商業銀行</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>已拜訪財務部</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1032,16 +1245,21 @@
           <t>臺灣土地銀行</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>可透過自營(不提供負責人ID)</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1049,16 +1267,21 @@
           <t>台中商業銀行</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>已聯繫但目前不開戶</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1066,16 +1289,21 @@
           <t>連線銀行</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>透過自營，目前不開複委託</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1083,16 +1311,21 @@
           <t>將來銀行</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>透過自營，目前不開複委託</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1100,16 +1333,21 @@
           <t>樂天銀行</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>已連繫，目前不做外幣債</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1117,20 +1355,25 @@
           <t>凱基商業銀行</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>總行 TIS，與銀行信託/財務部無關</t>
         </is>
@@ -1142,16 +1385,21 @@
           <t>渣打國際商業銀行</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1159,16 +1407,21 @@
           <t>三信商業銀行</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1176,21 +1429,26 @@
           <t>匯豐(台灣)銀行</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1202,142 +1460,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>開戶釐清需求說明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>請協助重新釐清各銀行的「開戶狀況」與「開戶主體單位」，須逐家確認以下四件事：</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>1. 客戶（銀行）主帳戶是否已在我司開戶？（是 / 否 / 申請中）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2. 若有開戶，開戶主體是哪個單位？請明確區分：</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 財務部（自營）：使用銀行自有資金做自營交易。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   • TMU（總行金融行銷部 / 交易室）：總行業務與交易員，背後資金來自客戶，與財務部自營資金性質不同。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>3. 該銀行是否設有 TMU 交易員？</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 並非所有銀行都有 TMU；部分小型銀行無 TMU，直接透過財務部交易。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 若無 TMU，請註明「無 TMU，走財務部」。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>4. 客戶是否與銀行財務部 / 信託相關？（是 / 否）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理（財務部）或信託部門通路，例如透過財務部代為下單、或信託名義交易。</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理或信託部門通路，例如代為下單、或信託名義交易。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
+      <c r="A17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>⚠️ 重點：請勿再使用「銀行」「自營&amp;TMU」等籠統標註，務必明確到「財務部」或「TMU」。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
+      <c r="A19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>特別需釐清：</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>【目前往來分類 A~G 圖例】</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>• 上海銀行：標「亞灣區」意義不明，須確認屬財務部或 TMU。</t>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>A：有實際交易往來（活躍）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>• 高雄、臺企銀、瑞興、永豐、第一：原僅標「銀行」，未區分主體，最需確認是否有 TMU。</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>B：已開戶但未 / 低度交易</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>• 自營&amp;TMU 六家（元大、王道、新光、合庫、兆豐、安泰）：須確認是否兩單位各自開戶，或僅業務同時接觸。</t>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>C：已開戶但有障礙待處理</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>D：B2B 已開戶（另一通路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>E：洽談 / 拜訪中（尚未開戶）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>F：初步接觸 / 待聯繫</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>G：暫不開戶 / 條件不符</t>
         </is>
       </c>
     </row>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="開戶釐清表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="依往來分類" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="釐清說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -35,17 +35,12 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00333333"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -58,8 +53,14 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,6 +89,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
@@ -104,11 +105,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,37 +146,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,17 +541,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="56" customHeight="1">
@@ -569,41 +561,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>目前往來
-分類(A~G)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>①主帳戶是否開戶
 (是/否/申請中)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>②開戶主體
 (財務部/TMU/兩者皆有)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>③是否有TMU交易員
 (有/無→走財務部)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>④客戶是否與銀行
 財務部/信託相關
 (是/否)</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>目前往來/交易狀況(原始資料)</t>
+        </is>
+      </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>目前往來/交易狀況(原始資料)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>業務備註</t>
         </is>
@@ -612,7 +598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【一】已開戶銀行（請逐家確認開戶主體）</t>
+          <t>A｜有實際交易往來（活躍）（11 家）</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -621,7 +607,6 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -629,21 +614,16 @@
           <t>聯邦銀行</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="6" t="inlineStr"/>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -651,804 +631,698 @@
           <t>華南銀行</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>上海銀行</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
+          <t>元大商業銀行</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>元大商業銀行</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+          <t>王道商業銀行</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>王道商業銀行</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>板信商銀</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營）</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>板信商銀</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>星展銀行</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>星展銀行</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 TMU）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
+          <t>陽信商業銀行</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營）</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>陽信商業銀行</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>新光銀行</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>新光銀行</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>台新銀行</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>台新銀行</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 TMU）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>兆豐銀行</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>華泰商業銀行</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>有開戶、久未交易（原標 自營）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
+          <t>臺灣中小企業銀行</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>已取得債券授權交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>京城銀行</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>有開戶（原標 自營）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B｜已開戶但未／低度交易（6 家）</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>合庫銀行</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>上海銀行</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>兆豐銀行</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>華泰商業銀行</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>有開戶、久未交易（原標 自營）</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>高雄銀行</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>有開戶（原標 銀行，未明確）</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
+          <t>京城銀行</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>有開戶（原標 自營）</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>臺灣中小企業銀行</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>已取得債券授權交易（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>高雄銀行</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>有開戶（原標 銀行，未明確）</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>瑞興商業銀行</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>已連繫（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>第一商業銀行</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>永豐商業銀行</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+          <t>瑞興商業銀行</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>信託部已開戶</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>安泰銀行</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C｜已開戶但有障礙待處理（2 家）</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>第一商業銀行</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>合庫銀行</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>【二】未開戶 / 進行中銀行（如有進展請補充開戶主體）</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>安泰銀行</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>臺灣銀行</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>待聯繫</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>D｜B2B 已開戶（另一通路）（4 家）</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>中華郵政</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
+          <t>凱基商業銀行</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>B2B已開戶</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>已連繫，待下次遴選</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>總行 TIS，與銀行信託/財務部無關</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>彰化商業銀行</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪財務部</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>渣打國際商業銀行</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>B2B已開戶</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>台北富邦銀行</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪財務部&amp;TMU</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>三信商業銀行</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>B2B已開戶</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>中國信託商業銀行</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪TMU</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>匯豐(台灣)銀行</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>B2B已開戶</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>遠東國際商業銀行</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪財務部&amp;信託基金</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>E｜洽談／拜訪中（尚未開戶）（7 家）</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>玉山商業銀行</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪財務部</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>台北富邦銀行</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>已拜訪財務部&amp;TMU</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>臺灣土地銀行</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>可透過自營(不提供負責人ID)</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
+          <t>中國信託商業銀行</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>已拜訪TMU</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>台中商業銀行</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>已聯繫但目前不開戶</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>遠東國際商業銀行</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>已拜訪財務部&amp;信託基金</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>連線銀行</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>透過自營，目前不開複委託</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
+          <t>彰化商業銀行</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>已拜訪財務部</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>將來銀行</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr"/>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>透過自營，目前不開複委託</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>玉山商業銀行</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>已拜訪財務部</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>樂天銀行</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>已連繫，目前不做外幣債</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
+          <t>中華郵政</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>已連繫，待下次遴選</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>凱基商業銀行</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr"/>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>永豐商業銀行</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>已連繫（原標 銀行）</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>B2B已開戶</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>總行 TIS，與銀行信託/財務部無關</t>
+          <t>信託部已開戶</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>渣打國際商業銀行</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>B2B已開戶</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>F｜初步接觸／待聯繫（1 家）</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>三信商業銀行</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr"/>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>B2B已開戶</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>臺灣銀行</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>待聯繫</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>匯豐(台灣)銀行</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>B2B已開戶</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>G｜暫不開戶／條件不符（5 家）</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>臺灣土地銀行</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>可透過自營(不提供負責人ID)</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>台中商業銀行</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>已聯繫但目前不開戶</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>連線銀行</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>透過自營，目前不開複委託</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>將來銀行</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>透過自營，目前不開複委託</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>樂天銀行</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>已連繫，目前不做外幣債</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="7">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1467,161 +1341,161 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>開戶釐清需求說明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>請協助重新釐清各銀行的「開戶狀況」與「開戶主體單位」，須逐家確認以下四件事：</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
+      <c r="A4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>1. 客戶（銀行）主帳戶是否已在我司開戶？（是 / 否 / 申請中）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
+      <c r="A6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>2. 若有開戶，開戶主體是哪個單位？請明確區分：</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 財務部（自營）：使用銀行自有資金做自營交易。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">   • TMU（總行金融行銷部 / 交易室）：總行業務與交易員，背後資金來自客戶，與財務部自營資金性質不同。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
+      <c r="A10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>3. 該銀行是否設有 TMU 交易員？</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 並非所有銀行都有 TMU；部分小型銀行無 TMU，直接透過財務部交易。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 若無 TMU，請註明「無 TMU，走財務部」。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
+      <c r="A14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>4. 客戶是否與銀行財務部 / 信託相關？（是 / 否）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">   • 確認該往來是否涉及銀行財富管理或信託部門通路，例如代為下單、或信託名義交易。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr"/>
+      <c r="A17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>⚠️ 重點：請勿再使用「銀行」「自營&amp;TMU」等籠統標註，務必明確到「財務部」或「TMU」。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
+      <c r="A19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>【目前往來分類 A~G 圖例】</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>【目前往來分類 A~G 說明】</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>A：有實際交易往來（活躍）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>B：已開戶但未 / 低度交易</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>C：已開戶但有障礙待處理</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>D：B2B 已開戶（另一通路）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>E：洽談 / 拜訪中（尚未開戶）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>F：初步接觸 / 待聯繫</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>G：暫不開戶 / 條件不符</t>
         </is>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="依往來分類" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="釐清說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="財務部自營vs TMU" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +61,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -107,6 +108,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -175,6 +181,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -798,7 +807,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>B｜已開戶但未／低度交易（6 家）</t>
+          <t>B｜已開戶但未／低度交易（7 家）</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
@@ -811,7 +820,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>上海銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
@@ -820,7 +829,7 @@
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
+          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -828,7 +837,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>華泰商業銀行</t>
+          <t>上海銀行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
@@ -837,7 +846,7 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>有開戶、久未交易（原標 自營）</t>
+          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -845,7 +854,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>京城銀行</t>
+          <t>華泰商業銀行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
@@ -854,7 +863,7 @@
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>有開戶（原標 自營）</t>
+          <t>有開戶、久未交易（原標 自營）</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -862,7 +871,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>高雄銀行</t>
+          <t>京城銀行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
@@ -871,7 +880,7 @@
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>有開戶（原標 銀行，未明確）</t>
+          <t>有開戶（原標 自營）</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -879,7 +888,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>第一商業銀行</t>
+          <t>高雄銀行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
@@ -888,7 +897,7 @@
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+          <t>有開戶（原標 銀行，未明確）</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -896,7 +905,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>瑞興商業銀行</t>
+          <t>第一商業銀行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -905,45 +914,45 @@
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
+          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>瑞興商業銀行</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>C｜已開戶但有障礙待處理（2 家）</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>合庫銀行</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>安泰銀行</t>
+          <t>合庫銀行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
@@ -952,70 +961,70 @@
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>安泰銀行</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
           <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>D｜B2B 已開戶（另一通路）（4 家）</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>凱基商業銀行</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>B2B已開戶</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>總行 TIS，與銀行信託/財務部無關</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>渣打國際商業銀行</t>
+          <t>凱基商業銀行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>B2B已開戶</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>總行 TIS，與銀行信託/財務部無關</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>三信商業銀行</t>
+          <t>渣打國際商業銀行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr"/>
@@ -1032,7 +1041,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>匯豐(台灣)銀行</t>
+          <t>三信商業銀行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
@@ -1047,39 +1056,39 @@
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>匯豐(台灣)銀行</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>B2B已開戶</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>E｜洽談／拜訪中（尚未開戶）（7 家）</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>台北富邦銀行</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>已拜訪財務部&amp;TMU</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>中國信託商業銀行</t>
+          <t>台北富邦銀行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -1088,7 +1097,7 @@
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>已拜訪TMU</t>
+          <t>已拜訪財務部&amp;TMU</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1096,7 +1105,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>遠東國際商業銀行</t>
+          <t>中國信託商業銀行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr"/>
@@ -1105,7 +1114,7 @@
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財務部&amp;信託基金</t>
+          <t>已拜訪TMU</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1113,7 +1122,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>彰化商業銀行</t>
+          <t>遠東國際商業銀行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr"/>
@@ -1122,7 +1131,7 @@
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>已拜訪財務部</t>
+          <t>已拜訪財務部&amp;信託基金</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1130,7 +1139,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>玉山商業銀行</t>
+          <t>彰化商業銀行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr"/>
@@ -1147,7 +1156,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>中華郵政</t>
+          <t>玉山商業銀行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr"/>
@@ -1156,7 +1165,7 @@
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>已連繫，待下次遴選</t>
+          <t>已拜訪財務部</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -1164,92 +1173,92 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>永豐商業銀行</t>
+          <t>中華郵政</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>已連繫，待下次遴選</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>永豐商業銀行</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>信託部已開戶</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>F｜初步接觸／待聯繫（1 家）</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>臺灣銀行</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>待聯繫</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>G｜暫不開戶／條件不符（5 家）</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>臺灣土地銀行</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>可透過自營(不提供負責人ID)</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>台中商業銀行</t>
+          <t>臺灣土地銀行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr"/>
@@ -1258,7 +1267,7 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>已聯繫但目前不開戶</t>
+          <t>可透過自營(不提供負責人ID)</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -1266,7 +1275,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>連線銀行</t>
+          <t>台中商業銀行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
@@ -1275,7 +1284,7 @@
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>透過自營，目前不開複委託</t>
+          <t>已聯繫但目前不開戶</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
@@ -1283,7 +1292,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>將來銀行</t>
+          <t>連線銀行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr"/>
@@ -1300,7 +1309,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>樂天銀行</t>
+          <t>將來銀行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr"/>
@@ -1309,20 +1318,37 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
+          <t>透過自營，目前不開複委託</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>樂天銀行</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
           <t>已連繫，目前不做外幣債</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1504,4 +1530,462 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>目前往來/交易狀況</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>備註（同時往來 / 說明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>【財務部自營】使用銀行自有資金做自營交易（11 家）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>華南銀行</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>板信商銀</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>陽信商業銀行</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>華泰商業銀行</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>有開戶、久未交易（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>京城銀行</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>有開戶（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>元大商業銀行</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>王道商業銀行</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>新光銀行</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>合庫銀行</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>兆豐銀行</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>安泰銀行</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>【總行 TMU】總行交易室，背後資金來自客戶（9 家）</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>聯邦銀行</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>星展銀行</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>台新銀行</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>元大商業銀行</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>王道商業銀行</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>新光銀行</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>合庫銀行</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>兆豐銀行</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>安泰銀行</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>財務部自營&amp;TMU 皆有</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>【尚待釐清主體】原僅標銀行／亞灣區／信託，須請業務確認（6 家）</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>上海銀行</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>高雄銀行</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>有開戶（原標 銀行，未明確）</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>臺灣中小企業銀行</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>已取得債券授權交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>瑞興商業銀行</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>已連繫（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>第一商業銀行</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>永豐銀行</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>已連繫（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>信託部已開戶（非財務部/TMU）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -1538,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1566,7 +1566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【財務部自營】使用銀行自有資金做自營交易（11 家）</t>
+          <t>【財務部自營】使用銀行自有資金做自營交易（3 家）</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -1575,12 +1575,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>華南銀行</t>
+          <t>陽信商業銀行</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
+          <t>有交易往來（原標 自營）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
@@ -1601,38 +1601,34 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>陽信商業銀行</t>
+          <t>臺灣中小企業銀行</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營）</t>
+          <t>已取得債券授權交易（原標 銀行）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>華泰商業銀行</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>有開戶、久未交易（原標 自營）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>【總行 TMU】總行交易室，背後資金來自客戶（9 家）</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>京城銀行</t>
+          <t>聯邦銀行</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>有開戶（原標 自營）</t>
+          <t>有交易往來（原標 TMU）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -1640,41 +1636,33 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>元大商業銀行</t>
+          <t>星展銀行</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>王道商業銀行</t>
+          <t>台新銀行</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>新光銀行</t>
+          <t>元大商業銀行</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1684,31 +1672,31 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>財務部自營&amp;TMU 皆有</t>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>合庫銀行</t>
+          <t>王道商業銀行</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>財務部自營&amp;TMU 皆有</t>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>兆豐銀行</t>
+          <t>新光銀行</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1718,71 +1706,79 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>財務部自營&amp;TMU 皆有</t>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>安泰銀行</t>
+          <t>合庫銀行</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>財務部自營&amp;TMU 皆有</t>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>【總行 TMU】總行交易室，背後資金來自客戶（9 家）</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>兆豐銀行</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>聯邦銀行</t>
+          <t>安泰銀行</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 TMU）</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
+          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>星展銀行</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 TMU）</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>【尚待釐清主體】原僅標銀行／亞灣區／信託／自營，須請業務確認（8 家）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>台新銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 TMU）</t>
+          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1790,191 +1786,93 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>元大商業銀行</t>
+          <t>華泰商業銀行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有開戶、久未交易（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>王道商業銀行</t>
+          <t>京城銀行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有開戶（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>新光銀行</t>
+          <t>上海銀行</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>合庫銀行</t>
+          <t>高雄銀行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有開戶（原標 銀行，未明確）</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>兆豐銀行</t>
+          <t>瑞興商業銀行</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>已連繫（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>安泰銀行</t>
+          <t>第一商業銀行</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>財務部自營&amp;TMU 皆有</t>
-        </is>
-      </c>
+          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>【尚待釐清主體】原僅標銀行／亞灣區／信託，須請業務確認（6 家）</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>上海銀行</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>高雄銀行</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>有開戶（原標 銀行，未明確）</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>臺灣中小企業銀行</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>已取得債券授權交易（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>瑞興商業銀行</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>永豐銀行</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>第一商業銀行</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>永豐銀行</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>已連繫（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>信託部已開戶（非財務部/TMU）</t>
         </is>
@@ -1982,9 +1880,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/銀行開戶釐清表.xlsx
+++ b/output/銀行開戶釐清表.xlsx
@@ -61,7 +61,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -108,11 +108,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -140,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,9 +176,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1538,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1566,7 +1558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【財務部自營】使用銀行自有資金做自營交易（3 家）</t>
+          <t>【財務部自營】使用銀行自有資金做自營交易（9 家）</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -1575,12 +1567,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>陽信商業銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營）</t>
+          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
@@ -1588,47 +1580,55 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>板信商銀</t>
+          <t>第一商業銀行</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
+          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>財務部往來；該行 TMU 不做交易</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>臺灣中小企業銀行</t>
+          <t>京城銀行</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>已取得債券授權交易（原標 銀行）</t>
+          <t>有開戶（原標 自營）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>【總行 TMU】總行交易室，背後資金來自客戶（9 家）</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>華泰商業銀行</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>有開戶、久未交易（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>聯邦銀行</t>
+          <t>高雄銀行</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 TMU）</t>
+          <t>有開戶（原標 銀行，未明確）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>星展銀行</t>
+          <t>瑞興商業銀行</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 TMU）</t>
+          <t>已連繫（原標 銀行）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -1649,12 +1649,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>台新銀行</t>
+          <t>陽信商業銀行</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 TMU）</t>
+          <t>有交易往來（原標 自營）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -1662,227 +1662,217 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>元大商業銀行</t>
+          <t>板信商銀</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>原自營&amp;TMU，現歸總行TMU</t>
-        </is>
-      </c>
+          <t>有交易往來（原標 自營）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>王道商業銀行</t>
+          <t>臺灣中小企業銀行</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>原自營&amp;TMU，現歸總行TMU</t>
-        </is>
-      </c>
+          <t>已取得債券授權交易（原標 銀行）</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>新光銀行</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>原自營&amp;TMU，現歸總行TMU</t>
-        </is>
-      </c>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>【總行 TMU】總行交易室，背後資金來自客戶（11 家）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>合庫銀行</t>
+          <t>聯邦銀行</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>原自營&amp;TMU，現歸總行TMU</t>
-        </is>
-      </c>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>兆豐銀行</t>
+          <t>星展銀行</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>有交易往來（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>原自營&amp;TMU，現歸總行TMU</t>
-        </is>
-      </c>
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>安泰銀行</t>
+          <t>台新銀行</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+          <t>有交易往來（原標 TMU）</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>元大商業銀行</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>原自營&amp;TMU，現歸總行TMU</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>【尚待釐清主體】原僅標銀行／亞灣區／信託／自營，須請業務確認（8 家）</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>華南銀行</t>
+          <t>王道商業銀行</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>有開戶，TMU 透過財務部下單（原標 自營）</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>華泰商業銀行</t>
+          <t>新光銀行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>有開戶、久未交易（原標 自營）</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>京城銀行</t>
+          <t>合庫銀行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>有開戶（原標 自營）</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
+          <t>有主帳，需新增子帳（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>上海銀行</t>
+          <t>兆豐銀行</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
+          <t>有交易往來（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>高雄銀行</t>
+          <t>安泰銀行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>有開戶（原標 銀行，未明確）</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
+          <t>有開戶，新負責人不願提供ID（原標 自營&amp;TMU）</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>原自營&amp;TMU，現歸總行TMU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>瑞興商業銀行</t>
+          <t>上海銀行</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>已連繫（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
+          <t>亞灣區有開戶（原標 亞灣區，需釐清）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>總行TMU，目前僅開亞灣區</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>第一商業銀行</t>
+          <t>永豐銀行</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>有股票戶，尚未有債券交易（原標 銀行）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>永豐銀行</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
           <t>已連繫（原標 銀行）</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>信託部已開戶（非財務部/TMU）</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>TMU 接觸中；信託部已開戶</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A16:C16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
